--- a/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{969E3855-BBB8-4851-B6CD-90F9DCCDD830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F694B32B-8B0F-4492-B275-31C9066F1204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{1B57EA14-E398-4498-836C-087A4CED9893}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FBD49357-E850-4519-BC41-7DA39330E3F5}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07EDF55F-4753-4261-B6E3-39396355A871}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91CC75CA-9962-4623-89ED-915036572496}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F694B32B-8B0F-4492-B275-31C9066F1204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55D8CFE1-EABD-49DF-B1CB-6DB441124A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FBD49357-E850-4519-BC41-7DA39330E3F5}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F990827F-D9A2-4753-946D-FD93AE5F65C3}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91CC75CA-9962-4623-89ED-915036572496}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81FA6D7-09D0-4BCC-A8F1-8EE92C1FDEDC}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-11_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55D8CFE1-EABD-49DF-B1CB-6DB441124A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5E5E91A-202F-4664-A59C-D2BB4276545B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F990827F-D9A2-4753-946D-FD93AE5F65C3}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{A383FC99-4790-45D2-AC2D-4B7AEE80F934}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81FA6D7-09D0-4BCC-A8F1-8EE92C1FDEDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB281C29-6B25-45CE-A192-DD4FAAFE3AA1}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
